--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/139.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/139.xlsx
@@ -426,13 +426,13 @@
         <v>-5.482063189734237</v>
       </c>
       <c r="E2">
-        <v>-12.35931711977189</v>
+        <v>-18.74746332038017</v>
       </c>
       <c r="F2">
-        <v>-1.229299858104183</v>
+        <v>-2.699555079087177</v>
       </c>
       <c r="G2">
-        <v>-7.149395707458683</v>
+        <v>-11.75993951127304</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.949526449868528</v>
       </c>
       <c r="E3">
-        <v>-13.05429749725505</v>
+        <v>-18.82069327355821</v>
       </c>
       <c r="F3">
-        <v>-1.567273758446381</v>
+        <v>-2.479790035491871</v>
       </c>
       <c r="G3">
-        <v>-5.717995269370764</v>
+        <v>-11.72079231027115</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.517126930900626</v>
       </c>
       <c r="E4">
-        <v>-11.46703565824853</v>
+        <v>-18.94611841814865</v>
       </c>
       <c r="F4">
-        <v>-2.116209641994335</v>
+        <v>-2.620248012310555</v>
       </c>
       <c r="G4">
-        <v>-6.888839220790344</v>
+        <v>-11.57157940172512</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.123870813103718</v>
       </c>
       <c r="E5">
-        <v>-15.2190393986677</v>
+        <v>-19.85097092351729</v>
       </c>
       <c r="F5">
-        <v>-1.963061076564762</v>
+        <v>-2.438791647625115</v>
       </c>
       <c r="G5">
-        <v>-6.400480785019216</v>
+        <v>-10.9417414917877</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.75942152112433</v>
       </c>
       <c r="E6">
-        <v>-13.66328215333255</v>
+        <v>-20.34436175207501</v>
       </c>
       <c r="F6">
-        <v>-1.832010039972269</v>
+        <v>-2.369905442775711</v>
       </c>
       <c r="G6">
-        <v>-6.414219549007191</v>
+        <v>-10.77417160822641</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.388498791543768</v>
       </c>
       <c r="E7">
-        <v>-14.9040659175382</v>
+        <v>-20.70155872485203</v>
       </c>
       <c r="F7">
-        <v>-1.972293231268963</v>
+        <v>-2.462833354756565</v>
       </c>
       <c r="G7">
-        <v>-5.807701121848395</v>
+        <v>-10.87951316728602</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.975327403680826</v>
       </c>
       <c r="E8">
-        <v>-16.20645051367018</v>
+        <v>-21.84253492192862</v>
       </c>
       <c r="F8">
-        <v>-1.837917956289035</v>
+        <v>-2.613647580845049</v>
       </c>
       <c r="G8">
-        <v>-5.457107728148498</v>
+        <v>-10.83095739586153</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.485178781713188</v>
       </c>
       <c r="E9">
-        <v>-16.68546796572755</v>
+        <v>-21.94390481259032</v>
       </c>
       <c r="F9">
-        <v>-1.385626040890894</v>
+        <v>-2.354112618241339</v>
       </c>
       <c r="G9">
-        <v>-4.965399020291627</v>
+        <v>-10.79803733101902</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.890698479018532</v>
       </c>
       <c r="E10">
-        <v>-17.31967622202777</v>
+        <v>-22.27506305982324</v>
       </c>
       <c r="F10">
-        <v>-1.278356604065372</v>
+        <v>-2.245312358455443</v>
       </c>
       <c r="G10">
-        <v>-4.751306040266959</v>
+        <v>-10.76218412282871</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.16120575868106</v>
       </c>
       <c r="E11">
-        <v>-19.1827130711534</v>
+        <v>-23.39515846325046</v>
       </c>
       <c r="F11">
-        <v>-1.03165139579622</v>
+        <v>-2.104847754697537</v>
       </c>
       <c r="G11">
-        <v>-4.313456597788491</v>
+        <v>-9.887074514977765</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.27168384456125</v>
       </c>
       <c r="E12">
-        <v>-18.47722663397244</v>
+        <v>-24.39396321885625</v>
       </c>
       <c r="F12">
-        <v>-0.8878965167143943</v>
+        <v>-2.093016183083352</v>
       </c>
       <c r="G12">
-        <v>-5.298916620099964</v>
+        <v>-9.585444089803689</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.20787019960488</v>
       </c>
       <c r="E13">
-        <v>-19.28612530359256</v>
+        <v>-24.35188916685098</v>
       </c>
       <c r="F13">
-        <v>-1.070320414526304</v>
+        <v>-1.936106829645069</v>
       </c>
       <c r="G13">
-        <v>-4.500303788024957</v>
+        <v>-8.703127424313751</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.972478515654707</v>
       </c>
       <c r="E14">
-        <v>-19.39547889392978</v>
+        <v>-25.57496206921263</v>
       </c>
       <c r="F14">
-        <v>-0.3054158951900743</v>
+        <v>-1.800269486199201</v>
       </c>
       <c r="G14">
-        <v>-3.307116964760836</v>
+        <v>-8.729711104994099</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.57395526676712</v>
       </c>
       <c r="E15">
-        <v>-22.47398986603218</v>
+        <v>-25.71431679985067</v>
       </c>
       <c r="F15">
-        <v>-0.09392955541834649</v>
+        <v>-1.399830056746697</v>
       </c>
       <c r="G15">
-        <v>-4.370897873440386</v>
+        <v>-7.940705476074057</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.031493178924881</v>
       </c>
       <c r="E16">
-        <v>-22.83262236506964</v>
+        <v>-26.54401475058802</v>
       </c>
       <c r="F16">
-        <v>-0.573538542658607</v>
+        <v>-1.486896440985342</v>
       </c>
       <c r="G16">
-        <v>-2.787761891105511</v>
+        <v>-8.247295098465962</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.376733585445688</v>
       </c>
       <c r="E17">
-        <v>-23.1154572661667</v>
+        <v>-27.66259764369668</v>
       </c>
       <c r="F17">
-        <v>-0.02664624149335945</v>
+        <v>-1.184987172258826</v>
       </c>
       <c r="G17">
-        <v>-3.293666218234777</v>
+        <v>-7.693848026847222</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.651601879157965</v>
       </c>
       <c r="E18">
-        <v>-23.36580036625874</v>
+        <v>-27.83089838019175</v>
       </c>
       <c r="F18">
-        <v>0.1841865163975595</v>
+        <v>-1.173903616409368</v>
       </c>
       <c r="G18">
-        <v>-1.518280235343346</v>
+        <v>-7.768272401115578</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.892940391299457</v>
       </c>
       <c r="E19">
-        <v>-26.12336932848952</v>
+        <v>-28.93105038408919</v>
       </c>
       <c r="F19">
-        <v>0.06177535181626538</v>
+        <v>-0.739799335707093</v>
       </c>
       <c r="G19">
-        <v>-2.488796455090549</v>
+        <v>-6.884439505768652</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.134239143484003</v>
       </c>
       <c r="E20">
-        <v>-26.05802797703285</v>
+        <v>-29.79803126133169</v>
       </c>
       <c r="F20">
-        <v>0.4786885238082426</v>
+        <v>-1.01476429792275</v>
       </c>
       <c r="G20">
-        <v>-2.031686258664601</v>
+        <v>-6.920911785974803</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.409970090934031</v>
       </c>
       <c r="E21">
-        <v>-27.83411359673719</v>
+        <v>-29.875556472106</v>
       </c>
       <c r="F21">
-        <v>0.1629803108858922</v>
+        <v>-0.4308381752805446</v>
       </c>
       <c r="G21">
-        <v>-1.881417286091542</v>
+        <v>-7.065211844940555</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.748034907065363</v>
       </c>
       <c r="E22">
-        <v>-24.23333371733017</v>
+        <v>-30.93619980452353</v>
       </c>
       <c r="F22">
-        <v>0.635613616227178</v>
+        <v>-0.1206833374265621</v>
       </c>
       <c r="G22">
-        <v>-0.5833887961442418</v>
+        <v>-7.255538418538795</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.162964745365371</v>
       </c>
       <c r="E23">
-        <v>-27.44767173881863</v>
+        <v>-31.17809050788024</v>
       </c>
       <c r="F23">
-        <v>0.2652240426786295</v>
+        <v>-0.07212775374406631</v>
       </c>
       <c r="G23">
-        <v>-0.6762330457931022</v>
+        <v>-6.409415947429708</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.662317530016421</v>
       </c>
       <c r="E24">
-        <v>-27.6853985103253</v>
+        <v>-31.28944568372886</v>
       </c>
       <c r="F24">
-        <v>0.7185166258993526</v>
+        <v>-0.1537550776159296</v>
       </c>
       <c r="G24">
-        <v>-0.3299731562041109</v>
+        <v>-6.677566825565135</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.25727981319631</v>
       </c>
       <c r="E25">
-        <v>-29.44607146874454</v>
+        <v>-31.5211382636203</v>
       </c>
       <c r="F25">
-        <v>1.4393967312464</v>
+        <v>0.02422214397775259</v>
       </c>
       <c r="G25">
-        <v>-0.9146353617126382</v>
+        <v>-6.306517570978081</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.947279496733124</v>
       </c>
       <c r="E26">
-        <v>-28.07659526595191</v>
+        <v>-31.74535659716208</v>
       </c>
       <c r="F26">
-        <v>1.815563339062072</v>
+        <v>-0.09656210702444332</v>
       </c>
       <c r="G26">
-        <v>-0.6423363700165046</v>
+        <v>-6.088554563218006</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.724179449311647</v>
       </c>
       <c r="E27">
-        <v>-30.58706125124315</v>
+        <v>-32.91624336505934</v>
       </c>
       <c r="F27">
-        <v>1.745223349420755</v>
+        <v>-0.08049757798195251</v>
       </c>
       <c r="G27">
-        <v>-1.112791375511254</v>
+        <v>-6.634794577197751</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.576927195021592</v>
       </c>
       <c r="E28">
-        <v>-30.15977708624942</v>
+        <v>-32.88860382395352</v>
       </c>
       <c r="F28">
-        <v>1.424066964090192</v>
+        <v>0.1699477091108388</v>
       </c>
       <c r="G28">
-        <v>-0.3473733835585203</v>
+        <v>-6.534299656807636</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.500350594226959</v>
       </c>
       <c r="E29">
-        <v>-31.09346917833591</v>
+        <v>-33.01762004843205</v>
       </c>
       <c r="F29">
-        <v>1.314677735080906</v>
+        <v>0.06265093616102446</v>
       </c>
       <c r="G29">
-        <v>-0.4522713295158671</v>
+        <v>-7.086614521851944</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.478582024180549</v>
       </c>
       <c r="E30">
-        <v>-29.46068711860429</v>
+        <v>-32.76269186840725</v>
       </c>
       <c r="F30">
-        <v>1.808170988359489</v>
+        <v>-0.1204257151642915</v>
       </c>
       <c r="G30">
-        <v>-1.113953376995539</v>
+        <v>-6.71011610930725</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.495310663008493</v>
       </c>
       <c r="E31">
-        <v>-29.53001805566173</v>
+        <v>-32.78874191513637</v>
       </c>
       <c r="F31">
-        <v>1.15362157442421</v>
+        <v>0.2296382074217656</v>
       </c>
       <c r="G31">
-        <v>-2.026018604701368</v>
+        <v>-7.049632417632745</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.53887261793445</v>
       </c>
       <c r="E32">
-        <v>-29.06875222171443</v>
+        <v>-31.65744985972518</v>
       </c>
       <c r="F32">
-        <v>1.100122294081807</v>
+        <v>0.08478905500084125</v>
       </c>
       <c r="G32">
-        <v>0.1546509841987196</v>
+        <v>-6.697867090811946</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.601739622866932</v>
       </c>
       <c r="E33">
-        <v>-30.50123308337578</v>
+        <v>-32.17519482149614</v>
       </c>
       <c r="F33">
-        <v>1.829047503644843</v>
+        <v>-0.09202099692229643</v>
       </c>
       <c r="G33">
-        <v>-1.16772987873546</v>
+        <v>-6.785434330871208</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.673779912017103</v>
       </c>
       <c r="E34">
-        <v>-27.60801141800822</v>
+        <v>-31.42168391746384</v>
       </c>
       <c r="F34">
-        <v>1.573361964361942</v>
+        <v>0.03850568310422447</v>
       </c>
       <c r="G34">
-        <v>-0.7740000766588589</v>
+        <v>-7.292570180941083</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.750745952916708</v>
       </c>
       <c r="E35">
-        <v>-29.82665574553417</v>
+        <v>-31.33607311634884</v>
       </c>
       <c r="F35">
-        <v>0.8240108713806753</v>
+        <v>0.05556259629526909</v>
       </c>
       <c r="G35">
-        <v>-1.136445223389347</v>
+        <v>-7.026180513032548</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.833960445659649</v>
       </c>
       <c r="E36">
-        <v>-27.38015219136427</v>
+        <v>-30.97110981064866</v>
       </c>
       <c r="F36">
-        <v>1.5272782290094</v>
+        <v>-0.03852254494729596</v>
       </c>
       <c r="G36">
-        <v>-1.99825968035458</v>
+        <v>-7.575496023818277</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.925592146336984</v>
       </c>
       <c r="E37">
-        <v>-27.49886160900134</v>
+        <v>-30.51965265140198</v>
       </c>
       <c r="F37">
-        <v>0.8805867082570759</v>
+        <v>-0.1093645252347097</v>
       </c>
       <c r="G37">
-        <v>-2.000805489874279</v>
+        <v>-6.649794659036189</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.024375293996676</v>
       </c>
       <c r="E38">
-        <v>-29.56353102755549</v>
+        <v>-29.63925616991175</v>
       </c>
       <c r="F38">
-        <v>0.7336591820225276</v>
+        <v>-0.3388355496886175</v>
       </c>
       <c r="G38">
-        <v>-0.6931896600452492</v>
+        <v>-7.271852786956324</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.133270416954542</v>
       </c>
       <c r="E39">
-        <v>-27.42569505445941</v>
+        <v>-29.11627855642493</v>
       </c>
       <c r="F39">
-        <v>0.9888228498416649</v>
+        <v>-0.06913486231775169</v>
       </c>
       <c r="G39">
-        <v>-1.868403531576667</v>
+        <v>-7.290405084158399</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.256100248658185</v>
       </c>
       <c r="E40">
-        <v>-27.71564418822253</v>
+        <v>-29.13486341375241</v>
       </c>
       <c r="F40">
-        <v>1.86737440663757</v>
+        <v>-0.1699687127909243</v>
       </c>
       <c r="G40">
-        <v>-0.0297265390654499</v>
+        <v>-6.833735190289175</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.392870612458705</v>
       </c>
       <c r="E41">
-        <v>-25.76657991837319</v>
+        <v>-28.15704813517218</v>
       </c>
       <c r="F41">
-        <v>1.151085113436838</v>
+        <v>-0.2514792368589929</v>
       </c>
       <c r="G41">
-        <v>-2.13421385401583</v>
+        <v>-6.535034597917353</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.540926085821352</v>
       </c>
       <c r="E42">
-        <v>-24.95841033306831</v>
+        <v>-28.06563183037934</v>
       </c>
       <c r="F42">
-        <v>1.221168309183287</v>
+        <v>-0.2510957027514967</v>
       </c>
       <c r="G42">
-        <v>-1.198700032255342</v>
+        <v>-7.68386342150078</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.70132376780227</v>
       </c>
       <c r="E43">
-        <v>-24.27478283992238</v>
+        <v>-27.74071382032899</v>
       </c>
       <c r="F43">
-        <v>1.096132876669924</v>
+        <v>-0.05023648839028377</v>
       </c>
       <c r="G43">
-        <v>-0.8131174827508872</v>
+        <v>-7.107706007482641</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.876393101520171</v>
       </c>
       <c r="E44">
-        <v>-24.85189156745989</v>
+        <v>-27.41681018845636</v>
       </c>
       <c r="F44">
-        <v>0.7885269253143556</v>
+        <v>-0.1424238399130351</v>
       </c>
       <c r="G44">
-        <v>-1.389115990583142</v>
+        <v>-6.507891435040869</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.063327497875709</v>
       </c>
       <c r="E45">
-        <v>-24.60469122832918</v>
+        <v>-26.37176971323226</v>
       </c>
       <c r="F45">
-        <v>1.50353556251036</v>
+        <v>-0.2098479762964981</v>
       </c>
       <c r="G45">
-        <v>-2.13321075871743</v>
+        <v>-7.017784969544956</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.261352768301184</v>
       </c>
       <c r="E46">
-        <v>-22.94579345899533</v>
+        <v>-26.35630950297008</v>
       </c>
       <c r="F46">
-        <v>1.467325966599188</v>
+        <v>-0.1549089934080293</v>
       </c>
       <c r="G46">
-        <v>-1.821506343467352</v>
+        <v>-6.470780219545639</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.474029585097697</v>
       </c>
       <c r="E47">
-        <v>-22.3473012771936</v>
+        <v>-26.11543997050209</v>
       </c>
       <c r="F47">
-        <v>1.204933964823222</v>
+        <v>-0.245219264396037</v>
       </c>
       <c r="G47">
-        <v>-1.592313965238068</v>
+        <v>-6.386930722126978</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.705662547697973</v>
       </c>
       <c r="E48">
-        <v>-20.88464945745615</v>
+        <v>-25.14714807275999</v>
       </c>
       <c r="F48">
-        <v>1.168240602348815</v>
+        <v>-0.4089435964571509</v>
       </c>
       <c r="G48">
-        <v>-1.578816871074459</v>
+        <v>-6.975472887007531</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.953090167526891</v>
       </c>
       <c r="E49">
-        <v>-20.89231163547712</v>
+        <v>-23.95793004207969</v>
       </c>
       <c r="F49">
-        <v>0.7631424346229676</v>
+        <v>-0.1334700166561753</v>
       </c>
       <c r="G49">
-        <v>-2.506067571168926</v>
+        <v>-7.126125882863145</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.220660467222574</v>
       </c>
       <c r="E50">
-        <v>-19.72668695437678</v>
+        <v>-24.68407537768364</v>
       </c>
       <c r="F50">
-        <v>1.605310438353113</v>
+        <v>-0.4109971192486909</v>
       </c>
       <c r="G50">
-        <v>-1.555798647939907</v>
+        <v>-6.990486211028126</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.514408933309134</v>
       </c>
       <c r="E51">
-        <v>-19.68995650170057</v>
+        <v>-23.2817700025724</v>
       </c>
       <c r="F51">
-        <v>1.173444406373202</v>
+        <v>-0.4617304808331466</v>
       </c>
       <c r="G51">
-        <v>-2.031795506667397</v>
+        <v>-7.094159255135943</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.837680491328704</v>
       </c>
       <c r="E52">
-        <v>-18.64919543441372</v>
+        <v>-23.73454947622933</v>
       </c>
       <c r="F52">
-        <v>1.137475037008842</v>
+        <v>-0.4158033069197336</v>
       </c>
       <c r="G52">
-        <v>-1.78203801954816</v>
+        <v>-6.309162696863959</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.184953569871406</v>
       </c>
       <c r="E53">
-        <v>-21.49433149853083</v>
+        <v>-22.28914208551308</v>
       </c>
       <c r="F53">
-        <v>1.516519393181839</v>
+        <v>-0.2968671435931834</v>
       </c>
       <c r="G53">
-        <v>-1.799924897096843</v>
+        <v>-6.799987489061844</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.559042074502132</v>
       </c>
       <c r="E54">
-        <v>-19.42908017106669</v>
+        <v>-22.33631519925099</v>
       </c>
       <c r="F54">
-        <v>1.854965462943634</v>
+        <v>-0.4303071917753502</v>
       </c>
       <c r="G54">
-        <v>-2.93643849127418</v>
+        <v>-6.650201856137519</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.962319588625286</v>
       </c>
       <c r="E55">
-        <v>-17.88387879864342</v>
+        <v>-21.67009968866455</v>
       </c>
       <c r="F55">
-        <v>1.234770101937255</v>
+        <v>-0.324728452818942</v>
       </c>
       <c r="G55">
-        <v>-2.982388863359264</v>
+        <v>-6.988036407329066</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.389610442526283</v>
       </c>
       <c r="E56">
-        <v>-19.0129768083979</v>
+        <v>-21.43851805638629</v>
       </c>
       <c r="F56">
-        <v>1.500321496987498</v>
+        <v>5.20398988686167E-05</v>
       </c>
       <c r="G56">
-        <v>-1.731810422626338</v>
+        <v>-7.091775662347668</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.83233602601255</v>
       </c>
       <c r="E57">
-        <v>-15.7147261635473</v>
+        <v>-20.92489400596232</v>
       </c>
       <c r="F57">
-        <v>1.242382798368982</v>
+        <v>-0.2644489852846247</v>
       </c>
       <c r="G57">
-        <v>-2.402533569973759</v>
+        <v>-6.830100211287055</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.289659742567313</v>
       </c>
       <c r="E58">
-        <v>-17.54062499733602</v>
+        <v>-20.63845443955514</v>
       </c>
       <c r="F58">
-        <v>1.189035937628694</v>
+        <v>-0.2005826868961856</v>
       </c>
       <c r="G58">
-        <v>-2.176201503090406</v>
+        <v>-7.582199878535302</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.76163857824114</v>
       </c>
       <c r="E59">
-        <v>-15.87457223907005</v>
+        <v>-20.51619469829606</v>
       </c>
       <c r="F59">
-        <v>1.512245017383394</v>
+        <v>-0.02299811145143043</v>
       </c>
       <c r="G59">
-        <v>-2.456243860802895</v>
+        <v>-7.076543842321481</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.237123762211541</v>
       </c>
       <c r="E60">
-        <v>-14.32668095308622</v>
+        <v>-19.24368897366668</v>
       </c>
       <c r="F60">
-        <v>1.823469277554391</v>
+        <v>-0.3893949541184853</v>
       </c>
       <c r="G60">
-        <v>-2.157549889522152</v>
+        <v>-7.444520910648091</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.708464503217078</v>
       </c>
       <c r="E61">
-        <v>-14.74894756887946</v>
+        <v>-19.50656236133793</v>
       </c>
       <c r="F61">
-        <v>1.163300219158519</v>
+        <v>-0.006811812400728087</v>
       </c>
       <c r="G61">
-        <v>-2.302846422695225</v>
+        <v>-7.345290618653976</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.17288179444772</v>
       </c>
       <c r="E62">
-        <v>-15.8284361458799</v>
+        <v>-19.57610160819972</v>
       </c>
       <c r="F62">
-        <v>1.324679443102308</v>
+        <v>-0.1330964229575127</v>
       </c>
       <c r="G62">
-        <v>-3.239823505584071</v>
+        <v>-8.142635511787441</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.6259062398033</v>
       </c>
       <c r="E63">
-        <v>-13.85354598876482</v>
+        <v>-19.72708093161545</v>
       </c>
       <c r="F63">
-        <v>1.4341001500729</v>
+        <v>-0.222044857935318</v>
       </c>
       <c r="G63">
-        <v>-3.802652663261104</v>
+        <v>-7.864056415203311</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.04938409602086</v>
       </c>
       <c r="E64">
-        <v>-14.36173134190559</v>
+        <v>-18.62522622149112</v>
       </c>
       <c r="F64">
-        <v>0.9933142578996438</v>
+        <v>-0.1184558574804343</v>
       </c>
       <c r="G64">
-        <v>-2.339418019267554</v>
+        <v>-7.422283976260807</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.4351633766056</v>
       </c>
       <c r="E65">
-        <v>-13.98308298775423</v>
+        <v>-18.28582615156424</v>
       </c>
       <c r="F65">
-        <v>1.251465018573276</v>
+        <v>-0.3689193686560872</v>
       </c>
       <c r="G65">
-        <v>-3.001629754033509</v>
+        <v>-7.262563396173129</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.77650335387833</v>
       </c>
       <c r="E66">
-        <v>-14.05892134196069</v>
+        <v>-19.16371159421721</v>
       </c>
       <c r="F66">
-        <v>0.9030685995690545</v>
+        <v>-0.4180614364597651</v>
       </c>
       <c r="G66">
-        <v>-2.48115902653145</v>
+        <v>-7.926149007337881</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.06224643773845</v>
       </c>
       <c r="E67">
-        <v>-12.66896964394238</v>
+        <v>-18.96708072433016</v>
       </c>
       <c r="F67">
-        <v>1.296021244435056</v>
+        <v>-0.729106769271757</v>
       </c>
       <c r="G67">
-        <v>-3.172427419495588</v>
+        <v>-7.872154009592368</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.27350730370901</v>
       </c>
       <c r="E68">
-        <v>-13.76177646299938</v>
+        <v>-18.61621908668987</v>
       </c>
       <c r="F68">
-        <v>1.329807037325637</v>
+        <v>-0.4135302667664518</v>
       </c>
       <c r="G68">
-        <v>-3.646722657815892</v>
+        <v>-7.915366560516475</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.4008491286513</v>
       </c>
       <c r="E69">
-        <v>-15.09875860054997</v>
+        <v>-19.19727211508806</v>
       </c>
       <c r="F69">
-        <v>1.556143519527351</v>
+        <v>-0.6812072525722784</v>
       </c>
       <c r="G69">
-        <v>-2.707941327608144</v>
+        <v>-7.958784365264017</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.44327782566059</v>
       </c>
       <c r="E70">
-        <v>-14.73131369109359</v>
+        <v>-18.3359790011992</v>
       </c>
       <c r="F70">
-        <v>1.155830001920073</v>
+        <v>-0.6558037094306259</v>
       </c>
       <c r="G70">
-        <v>-2.489773066024633</v>
+        <v>-7.685942444099442</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.39419863772787</v>
       </c>
       <c r="E71">
-        <v>-12.73107766495758</v>
+        <v>-18.03640686016978</v>
       </c>
       <c r="F71">
-        <v>0.5696043313676967</v>
+        <v>-0.491178942002669</v>
       </c>
       <c r="G71">
-        <v>-3.444054370447249</v>
+        <v>-7.898803901183501</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.24865777038754</v>
       </c>
       <c r="E72">
-        <v>-13.34969438524939</v>
+        <v>-18.18493175067335</v>
       </c>
       <c r="F72">
-        <v>0.6328104209361046</v>
+        <v>-0.5717964860105197</v>
       </c>
       <c r="G72">
-        <v>-2.935110962512933</v>
+        <v>-7.755785023341446</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.00962769644616</v>
       </c>
       <c r="E73">
-        <v>-13.14010302275239</v>
+        <v>-19.08912309883688</v>
       </c>
       <c r="F73">
-        <v>1.038755180147614</v>
+        <v>-0.8557732572012322</v>
       </c>
       <c r="G73">
-        <v>-3.586020494807816</v>
+        <v>-7.846109947834922</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.68999607789853</v>
       </c>
       <c r="E74">
-        <v>-14.63965737717834</v>
+        <v>-18.79493078492857</v>
       </c>
       <c r="F74">
-        <v>0.7454816415952822</v>
+        <v>-1.210621829905859</v>
       </c>
       <c r="G74">
-        <v>-4.000907993425899</v>
+        <v>-6.982050940994063</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.294349845416</v>
       </c>
       <c r="E75">
-        <v>-15.09701060958301</v>
+        <v>-18.68110306227177</v>
       </c>
       <c r="F75">
-        <v>0.4673871073318489</v>
+        <v>-1.049322129232739</v>
       </c>
       <c r="G75">
-        <v>-2.802841426036892</v>
+        <v>-7.545717666692533</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.83010856905664</v>
       </c>
       <c r="E76">
-        <v>-13.02798706327048</v>
+        <v>-18.46532127580628</v>
       </c>
       <c r="F76">
-        <v>0.790934160986891</v>
+        <v>-1.005290259936932</v>
       </c>
       <c r="G76">
-        <v>-3.288422314100572</v>
+        <v>-7.325430655963888</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.3121757332385</v>
       </c>
       <c r="E77">
-        <v>-13.89304786753373</v>
+        <v>-19.23231797543342</v>
       </c>
       <c r="F77">
-        <v>0.3430127120059199</v>
+        <v>-1.322784432979718</v>
       </c>
       <c r="G77">
-        <v>-1.618629491729735</v>
+        <v>-7.277364845279211</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.758019745676007</v>
       </c>
       <c r="E78">
-        <v>-13.26793278704091</v>
+        <v>-19.49059043351288</v>
       </c>
       <c r="F78">
-        <v>0.2390244384628868</v>
+        <v>-1.363830037788433</v>
       </c>
       <c r="G78">
-        <v>-2.916204436938155</v>
+        <v>-7.192306998738716</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.175260354565513</v>
       </c>
       <c r="E79">
-        <v>-15.31273805436041</v>
+        <v>-19.70105579149337</v>
       </c>
       <c r="F79">
-        <v>0.4478558607086421</v>
+        <v>-1.328935060945504</v>
       </c>
       <c r="G79">
-        <v>-1.678060405250731</v>
+        <v>-6.646848273506238</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.571602990446387</v>
       </c>
       <c r="E80">
-        <v>-15.03398330834425</v>
+        <v>-20.20019778204082</v>
       </c>
       <c r="F80">
-        <v>-0.001898765334724219</v>
+        <v>-1.199603715081223</v>
       </c>
       <c r="G80">
-        <v>-1.675445074274707</v>
+        <v>-6.509556639447123</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.963045155470538</v>
       </c>
       <c r="E81">
-        <v>-16.8411840729553</v>
+        <v>-21.03273055750697</v>
       </c>
       <c r="F81">
-        <v>0.02184887136873201</v>
+        <v>-1.485086458210225</v>
       </c>
       <c r="G81">
-        <v>-0.7261759357985473</v>
+        <v>-6.1403646009076</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.360038708838771</v>
       </c>
       <c r="E82">
-        <v>-16.73792128015839</v>
+        <v>-21.61055478393769</v>
       </c>
       <c r="F82">
-        <v>-0.2851366328021396</v>
+        <v>-1.707194953188051</v>
       </c>
       <c r="G82">
-        <v>-1.084979482435837</v>
+        <v>-5.832603045394793</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.767072528806666</v>
       </c>
       <c r="E83">
-        <v>-17.16599339962946</v>
+        <v>-21.96613509149397</v>
       </c>
       <c r="F83">
-        <v>-0.6465914355440927</v>
+        <v>-1.550838120807436</v>
       </c>
       <c r="G83">
-        <v>-0.9722587173691924</v>
+        <v>-6.217530106882472</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.186195839363849</v>
       </c>
       <c r="E84">
-        <v>-16.09667124677624</v>
+        <v>-23.18827512821004</v>
       </c>
       <c r="F84">
-        <v>-0.04623878730437336</v>
+        <v>-1.856823785523128</v>
       </c>
       <c r="G84">
-        <v>-0.6445908515287482</v>
+        <v>-6.083330522357036</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.631993954262269</v>
       </c>
       <c r="E85">
-        <v>-19.09001973669039</v>
+        <v>-23.8040796661431</v>
       </c>
       <c r="F85">
-        <v>-0.3557947155261318</v>
+        <v>-1.958771790153066</v>
       </c>
       <c r="G85">
-        <v>0.06139291635745025</v>
+        <v>-6.041601095834523</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.107951155907536</v>
       </c>
       <c r="E86">
-        <v>-20.20665085750175</v>
+        <v>-24.88051605166237</v>
       </c>
       <c r="F86">
-        <v>-0.5144436405102931</v>
+        <v>-1.628929144236748</v>
       </c>
       <c r="G86">
-        <v>-0.8770904647517637</v>
+        <v>-5.688236775518255</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.614865456852497</v>
       </c>
       <c r="E87">
-        <v>-19.58991345392312</v>
+        <v>-25.39105621128713</v>
       </c>
       <c r="F87">
-        <v>-1.37129445645506</v>
+        <v>-2.100523676854923</v>
       </c>
       <c r="G87">
-        <v>-1.093282330648329</v>
+        <v>-5.390721358449492</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.155614357091164</v>
       </c>
       <c r="E88">
-        <v>-21.85625619817186</v>
+        <v>-26.33954962066769</v>
       </c>
       <c r="F88">
-        <v>-1.167516903733784</v>
+        <v>-1.783142161778918</v>
       </c>
       <c r="G88">
-        <v>-0.6621367428868855</v>
+        <v>-6.21881128800617</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.740943027752839</v>
       </c>
       <c r="E89">
-        <v>-24.33365300202209</v>
+        <v>-27.7434943033697</v>
       </c>
       <c r="F89">
-        <v>-1.094121066743539</v>
+        <v>-2.340710462031446</v>
       </c>
       <c r="G89">
-        <v>0.187994798870259</v>
+        <v>-5.277285515546366</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.372661405743789</v>
       </c>
       <c r="E90">
-        <v>-25.2151612238812</v>
+        <v>-28.90360783160271</v>
       </c>
       <c r="F90">
-        <v>-1.510040197852157</v>
+        <v>-2.554496349713345</v>
       </c>
       <c r="G90">
-        <v>-0.5147678082062286</v>
+        <v>-5.646464311903731</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.052998815214739</v>
       </c>
       <c r="E91">
-        <v>-27.80030853826993</v>
+        <v>-29.98157936981059</v>
       </c>
       <c r="F91">
-        <v>-1.383921260775933</v>
+        <v>-2.658197179767606</v>
       </c>
       <c r="G91">
-        <v>-0.9736623886778435</v>
+        <v>-5.666565944418186</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.790068107931146</v>
       </c>
       <c r="E92">
-        <v>-29.0993737629543</v>
+        <v>-31.03461713013223</v>
       </c>
       <c r="F92">
-        <v>-1.699824140037941</v>
+        <v>-2.633226044410216</v>
       </c>
       <c r="G92">
-        <v>-0.6420152470991952</v>
+        <v>-5.695953657170296</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.593094226304268</v>
       </c>
       <c r="E93">
-        <v>-31.60501013071636</v>
+        <v>-32.40722477270116</v>
       </c>
       <c r="F93">
-        <v>-1.07744437419038</v>
+        <v>-2.532590173746312</v>
       </c>
       <c r="G93">
-        <v>-0.615997669706063</v>
+        <v>-5.998441513639044</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.464161328671391</v>
       </c>
       <c r="E94">
-        <v>-33.68693529947674</v>
+        <v>-34.71254635697093</v>
       </c>
       <c r="F94">
-        <v>-2.280358098165682</v>
+        <v>-3.082570628589196</v>
       </c>
       <c r="G94">
-        <v>-0.4122203495817643</v>
+        <v>-5.50147897001135</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.40716538764214</v>
       </c>
       <c r="E95">
-        <v>-33.35608725271334</v>
+        <v>-36.68208159357194</v>
       </c>
       <c r="F95">
-        <v>-1.187153353017147</v>
+        <v>-2.691686417127985</v>
       </c>
       <c r="G95">
-        <v>-1.216126743974065</v>
+        <v>-6.331853175990124</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.432362228289709</v>
       </c>
       <c r="E96">
-        <v>-36.54682286767383</v>
+        <v>-38.03749462033375</v>
       </c>
       <c r="F96">
-        <v>-2.386000621412106</v>
+        <v>-3.353308431948367</v>
       </c>
       <c r="G96">
-        <v>-0.2910179668435069</v>
+        <v>-6.436711395400999</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.536805352401901</v>
       </c>
       <c r="E97">
-        <v>-37.09753738445764</v>
+        <v>-40.1495748975112</v>
       </c>
       <c r="F97">
-        <v>-2.411325469650492</v>
+        <v>-3.331741058249079</v>
       </c>
       <c r="G97">
-        <v>-0.8559095943915066</v>
+        <v>-6.629921454163944</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.722871790901889</v>
       </c>
       <c r="E98">
-        <v>-38.68824086370998</v>
+        <v>-42.14819652266348</v>
       </c>
       <c r="F98">
-        <v>-1.982587352983552</v>
+        <v>-3.524435055120897</v>
       </c>
       <c r="G98">
-        <v>-1.212293132239589</v>
+        <v>-6.878533492526593</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.971606784224913</v>
       </c>
       <c r="E99">
-        <v>-41.42597963826118</v>
+        <v>-43.93899741865575</v>
       </c>
       <c r="F99">
-        <v>-3.085926344937937</v>
+        <v>-3.659410896467854</v>
       </c>
       <c r="G99">
-        <v>-1.625558463543429</v>
+        <v>-6.880827700585307</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.294415431122165</v>
       </c>
       <c r="E100">
-        <v>-43.72314770508014</v>
+        <v>-45.83646651989869</v>
       </c>
       <c r="F100">
-        <v>-2.799164602539012</v>
+        <v>-3.76846877851602</v>
       </c>
       <c r="G100">
-        <v>-1.995177562457518</v>
+        <v>-7.724934049460979</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.643854915187595</v>
       </c>
       <c r="E101">
-        <v>-45.31446026408651</v>
+        <v>-47.7096494150385</v>
       </c>
       <c r="F101">
-        <v>-3.151857763261555</v>
+        <v>-4.017121478549154</v>
       </c>
       <c r="G101">
-        <v>-1.754302269020146</v>
+        <v>-7.209902548279942</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.051179930131386</v>
       </c>
       <c r="E102">
-        <v>-48.0909197556403</v>
+        <v>-50.30868555920876</v>
       </c>
       <c r="F102">
-        <v>-3.393278815868249</v>
+        <v>-3.907430723805248</v>
       </c>
       <c r="G102">
-        <v>-2.93980200554208</v>
+        <v>-7.935547646123872</v>
       </c>
     </row>
   </sheetData>
